--- a/data/trans_camb/P5_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P5_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-20,22; 7,87</t>
+          <t>-21,71; 9,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,38; 6,04</t>
+          <t>-25,09; 4,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-40,32; -12,88</t>
+          <t>-40,09; -14,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-22,03; 8,57</t>
+          <t>-21,46; 8,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,5; 14,76</t>
+          <t>-17,13; 14,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-33,45; -4,13</t>
+          <t>-32,81; -2,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-17,45; 4,15</t>
+          <t>-16,49; 4,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-17,55; 4,24</t>
+          <t>-16,49; 5,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-32,17; -12,23</t>
+          <t>-31,38; -11,41</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-43,22; 23,91</t>
+          <t>-45,94; 27,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-54,19; 18,67</t>
+          <t>-53,38; 13,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-82,98; -36,86</t>
+          <t>-83,07; -39,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-43,81; 25,81</t>
+          <t>-43,42; 24,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,1; 41,53</t>
+          <t>-36,16; 42,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-67,1; -10,71</t>
+          <t>-67,31; -7,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,42; 11,03</t>
+          <t>-34,81; 11,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,35; 11,16</t>
+          <t>-35,63; 14,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-69,63; -31,5</t>
+          <t>-69,0; -30,85</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,4; 17,45</t>
+          <t>5,98; 17,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 13,58</t>
+          <t>2,08; 13,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 10,73</t>
+          <t>-10,64; 11,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,63; 16,47</t>
+          <t>4,18; 15,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 13,4</t>
+          <t>2,11; 13,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,86; -6,04</t>
+          <t>-16,0; -6,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,27; 15,36</t>
+          <t>6,77; 14,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,74; 12,11</t>
+          <t>4,27; 12,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 0,72</t>
+          <t>-11,53; 0,05</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,09; 73,38</t>
+          <t>19,01; 75,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,9; 57,41</t>
+          <t>7,06; 57,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-40,17; 44,71</t>
+          <t>-39,22; 46,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,31; 66,96</t>
+          <t>14,39; 66,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,59; 55,61</t>
+          <t>7,46; 56,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-53,72; -24,57</t>
+          <t>-55,02; -26,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,86; 61,74</t>
+          <t>23,32; 60,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,33; 49,79</t>
+          <t>14,9; 49,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-42,22; 3,56</t>
+          <t>-41,05; 6,25</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,89; 23,32</t>
+          <t>4,18; 23,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 20,42</t>
+          <t>1,84; 20,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,53; 1,41</t>
+          <t>-14,82; 1,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,21; 26,22</t>
+          <t>7,66; 25,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,02; 26,85</t>
+          <t>8,76; 27,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,03; 1,9</t>
+          <t>-13,99; 1,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,65; 21,85</t>
+          <t>8,3; 21,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,54; 21,16</t>
+          <t>7,79; 20,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,02; -0,27</t>
+          <t>-12,39; -1,16</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,82; 107,72</t>
+          <t>13,65; 107,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,9; 91,5</t>
+          <t>6,37; 94,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-48,44; 5,22</t>
+          <t>-47,68; 6,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25,49; 125,82</t>
+          <t>27,06; 128,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30,81; 134,31</t>
+          <t>29,5; 129,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-50,96; 10,49</t>
+          <t>-48,62; 7,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,06; 98,19</t>
+          <t>27,33; 94,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26,59; 95,95</t>
+          <t>26,46; 90,52</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-41,72; -1,24</t>
+          <t>-42,36; -3,95</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,77; 15,16</t>
+          <t>5,33; 14,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,59; 11,98</t>
+          <t>2,16; 11,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 3,41</t>
+          <t>-12,01; 3,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,53; 14,66</t>
+          <t>5,97; 15,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,85; 14,0</t>
+          <t>4,84; 14,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,08; -7,06</t>
+          <t>-14,63; -6,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,89; 13,26</t>
+          <t>7,16; 13,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,0; 11,5</t>
+          <t>5,08; 11,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-12,34; -2,76</t>
+          <t>-12,06; -4,0</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>15,67; 59,94</t>
+          <t>17,53; 56,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,85; 46,3</t>
+          <t>6,97; 43,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-41,54; 14,36</t>
+          <t>-41,05; 18,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17,91; 57,26</t>
+          <t>19,69; 58,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,63; 55,17</t>
+          <t>15,97; 56,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-49,57; -26,22</t>
+          <t>-48,83; -26,66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,88; 49,8</t>
+          <t>24,1; 51,63</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,61; 43,42</t>
+          <t>17,33; 43,63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-41,93; -8,34</t>
+          <t>-41,32; -14,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P5_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P5_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-21,71; 9,34</t>
+          <t>-22,26; 8,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,09; 4,6</t>
+          <t>-25,79; 4,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-40,09; -14,99</t>
+          <t>-40,16; -13,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-21,46; 8,99</t>
+          <t>-21,53; 9,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,13; 14,34</t>
+          <t>-15,76; 14,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-32,81; -2,78</t>
+          <t>-32,68; -3,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-16,49; 4,16</t>
+          <t>-16,11; 5,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-16,49; 5,76</t>
+          <t>-15,95; 7,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-31,38; -11,41</t>
+          <t>-32,05; -11,76</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-45,94; 27,44</t>
+          <t>-46,84; 24,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-53,38; 13,44</t>
+          <t>-54,47; 12,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-83,07; -39,87</t>
+          <t>-84,88; -36,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-43,42; 24,91</t>
+          <t>-42,11; 27,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-36,16; 42,83</t>
+          <t>-32,55; 42,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-67,31; -7,7</t>
+          <t>-66,81; -10,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-34,81; 11,45</t>
+          <t>-34,75; 16,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,63; 14,84</t>
+          <t>-33,92; 19,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-69,0; -30,85</t>
+          <t>-68,56; -30,63</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,98; 17,96</t>
+          <t>5,63; 17,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 13,72</t>
+          <t>2,09; 13,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 11,8</t>
+          <t>-10,5; 11,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,18; 15,66</t>
+          <t>4,28; 15,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,11; 13,63</t>
+          <t>2,68; 13,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,0; -6,32</t>
+          <t>-15,94; -6,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,77; 14,97</t>
+          <t>7,03; 15,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,27; 12,22</t>
+          <t>4,18; 11,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 0,05</t>
+          <t>-11,6; -0,37</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,01; 75,73</t>
+          <t>19,7; 76,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,06; 57,61</t>
+          <t>6,71; 58,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-39,22; 46,73</t>
+          <t>-37,97; 50,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,39; 66,78</t>
+          <t>14,56; 65,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,46; 56,4</t>
+          <t>9,25; 56,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-55,02; -26,27</t>
+          <t>-54,25; -26,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,32; 60,8</t>
+          <t>24,72; 61,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,9; 49,88</t>
+          <t>14,29; 49,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-41,05; 6,25</t>
+          <t>-41,37; 0,07</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,18; 23,57</t>
+          <t>4,14; 22,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,84; 20,87</t>
+          <t>2,85; 20,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,82; 1,48</t>
+          <t>-13,77; 2,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,66; 25,45</t>
+          <t>7,06; 26,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,76; 27,58</t>
+          <t>7,9; 26,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 1,26</t>
+          <t>-15,3; 1,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,3; 21,56</t>
+          <t>8,72; 22,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,79; 20,62</t>
+          <t>7,43; 21,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,39; -1,16</t>
+          <t>-12,76; -0,69</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,65; 107,47</t>
+          <t>12,62; 102,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,37; 94,1</t>
+          <t>9,7; 95,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-47,68; 6,5</t>
+          <t>-46,62; 8,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27,06; 128,11</t>
+          <t>25,36; 132,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29,5; 129,86</t>
+          <t>26,62; 132,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,62; 7,92</t>
+          <t>-49,51; 9,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,33; 94,81</t>
+          <t>29,35; 96,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26,46; 90,52</t>
+          <t>23,85; 92,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-42,36; -3,95</t>
+          <t>-44,04; -3,06</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,33; 14,83</t>
+          <t>5,19; 15,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,16; 11,33</t>
+          <t>1,97; 11,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 3,93</t>
+          <t>-12,15; 3,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,97; 15,08</t>
+          <t>5,91; 14,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,84; 14,03</t>
+          <t>5,17; 14,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,63; -6,85</t>
+          <t>-14,75; -6,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,16; 13,57</t>
+          <t>6,82; 13,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,08; 11,51</t>
+          <t>4,87; 11,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-12,06; -4,0</t>
+          <t>-12,44; -3,56</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,53; 56,42</t>
+          <t>17,01; 59,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,97; 43,22</t>
+          <t>6,6; 44,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-41,05; 18,05</t>
+          <t>-41,18; 14,99</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19,69; 58,15</t>
+          <t>19,92; 57,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,97; 56,1</t>
+          <t>16,86; 55,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-48,83; -26,66</t>
+          <t>-49,41; -26,73</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,1; 51,63</t>
+          <t>23,0; 50,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>17,33; 43,63</t>
+          <t>16,82; 43,64</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-41,32; -14,38</t>
+          <t>-42,03; -12,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P5_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P5_R-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-6,15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,51</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-18,28</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-6,59</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-10,79</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-27,25</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-6,15</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,51</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-18,2</t>
+          <t>-23,29</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-22,38</t>
+          <t>-20,47</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-22,26; 8,06</t>
+          <t>-22,03; 8,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,79; 4,51</t>
+          <t>-16,5; 14,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-40,16; -13,47</t>
+          <t>-33,24; -3,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-21,53; 9,12</t>
+          <t>-20,22; 7,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,76; 14,98</t>
+          <t>-25,38; 6,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-32,68; -3,66</t>
+          <t>-36,36; -8,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-16,11; 5,07</t>
+          <t>-17,45; 4,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-15,95; 7,17</t>
+          <t>-17,55; 4,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-32,05; -11,76</t>
+          <t>-30,58; -9,8</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-14,59%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-3,59%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-43,4%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-16,05%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-26,29%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-66,39%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-14,59%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-3,59%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-43,19%</t>
+          <t>-56,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-53,84%</t>
+          <t>-49,24%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-46,84; 24,54</t>
+          <t>-43,81; 25,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-54,47; 12,66</t>
+          <t>-34,1; 41,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-84,88; -36,14</t>
+          <t>-66,78; -6,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-42,11; 27,76</t>
+          <t>-43,22; 23,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,55; 42,11</t>
+          <t>-54,19; 18,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-66,81; -10,7</t>
+          <t>-76,56; -22,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-34,75; 16,58</t>
+          <t>-37,42; 11,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-33,92; 19,22</t>
+          <t>-38,35; 11,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-68,56; -30,63</t>
+          <t>-65,19; -25,79</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10,3</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8,14</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-10,81</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>11,6</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>7,9</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-3,79</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10,3</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,14</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-11,13</t>
+          <t>-8,44</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-7,67</t>
+          <t>-9,69</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,63; 17,54</t>
+          <t>4,63; 16,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 13,6</t>
+          <t>2,29; 13,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 11,48</t>
+          <t>-15,61; -5,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,28; 15,65</t>
+          <t>5,4; 17,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,68; 13,53</t>
+          <t>2,22; 13,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,94; -6,57</t>
+          <t>-13,63; -3,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,03; 15,14</t>
+          <t>7,27; 15,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,18; 11,98</t>
+          <t>3,74; 12,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-11,6; -0,37</t>
+          <t>-13,19; -5,91</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>38,37%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>30,31%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-40,26%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>44,14%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>30,06%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-14,43%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>38,37%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>30,31%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-41,42%</t>
+          <t>-32,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-28,86%</t>
+          <t>-36,44%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,7; 76,07</t>
+          <t>13,31; 66,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,71; 58,41</t>
+          <t>7,59; 55,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-37,97; 50,36</t>
+          <t>-53,04; -23,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,56; 65,37</t>
+          <t>18,09; 73,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,25; 56,45</t>
+          <t>7,9; 57,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,25; -26,87</t>
+          <t>-47,15; -14,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,72; 61,78</t>
+          <t>24,86; 61,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,29; 49,05</t>
+          <t>13,33; 49,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-41,37; 0,07</t>
+          <t>-46,3; -23,71</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>16,91</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>17,51</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-6,19</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>13,25</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>11,62</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-6,84</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>16,91</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>17,51</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-6,42</t>
+          <t>-6,77</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-6,74</t>
+          <t>-6,56</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,14; 22,94</t>
+          <t>8,21; 26,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,85; 20,52</t>
+          <t>9,02; 26,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,77; 2,07</t>
+          <t>-15,2; 2,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,06; 26,05</t>
+          <t>3,89; 23,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,9; 26,42</t>
+          <t>1,86; 20,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,3; 1,53</t>
+          <t>-14,55; 1,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,72; 22,05</t>
+          <t>8,65; 21,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,43; 21,08</t>
+          <t>7,54; 21,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,76; -0,69</t>
+          <t>-12,2; -0,25</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>67,32%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>69,7%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-24,64%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>49,25%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>43,18%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-25,43%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>67,32%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>69,7%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-25,56%</t>
+          <t>-25,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-25,88%</t>
+          <t>-25,17%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,62; 102,33</t>
+          <t>25,49; 125,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,7; 95,02</t>
+          <t>30,81; 134,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-46,62; 8,76</t>
+          <t>-50,91; 10,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25,36; 132,86</t>
+          <t>12,82; 107,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,62; 132,19</t>
+          <t>4,9; 91,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-49,51; 9,14</t>
+          <t>-48,35; 6,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,35; 96,44</t>
+          <t>29,06; 98,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23,85; 92,85</t>
+          <t>26,59; 95,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-44,04; -3,06</t>
+          <t>-41,25; -0,96</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>10,33</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9,44</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-10,57</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>9,93</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>6,89</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-6,88</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>10,33</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9,44</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-10,82</t>
+          <t>-9,72</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-8,99</t>
+          <t>-10,17</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,19; 15,21</t>
+          <t>5,53; 14,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,97; 11,23</t>
+          <t>4,85; 14,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 3,72</t>
+          <t>-14,77; -6,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,91; 14,63</t>
+          <t>4,77; 15,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,17; 14,24</t>
+          <t>2,59; 11,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,75; -6,74</t>
+          <t>-14,13; -5,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,82; 13,54</t>
+          <t>6,89; 13,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,87; 11,43</t>
+          <t>5,0; 11,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-12,44; -3,56</t>
+          <t>-13,04; -7,14</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>36,97%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>33,78%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-37,83%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>35,34%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>24,53%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-24,48%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>36,97%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>33,78%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-38,75%</t>
+          <t>-34,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-32,08%</t>
+          <t>-36,3%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,01; 59,31</t>
+          <t>17,91; 57,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,6; 44,69</t>
+          <t>15,63; 55,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-41,18; 14,99</t>
+          <t>-48,51; -25,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19,92; 57,51</t>
+          <t>15,67; 59,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,86; 55,33</t>
+          <t>7,85; 46,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-49,41; -26,73</t>
+          <t>-45,9; -20,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,0; 50,72</t>
+          <t>22,88; 49,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,82; 43,64</t>
+          <t>16,61; 43,42</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-42,03; -12,02</t>
+          <t>-44,25; -27,12</t>
         </is>
       </c>
     </row>
